--- a/data/basketball_scp_master.xlsx
+++ b/data/basketball_scp_master.xlsx
@@ -1026,11 +1026,6 @@
           <t>2019 Hoops Winter</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/basketball-cards-2019-panini-hoops-winter</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1174,11 +1169,6 @@
           <t>2019 Panini Eminence</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/basketball-cards-2019-panini-eminence</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1543,11 +1533,6 @@
           <t>2020 Hoops Winter</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/basketball-cards-2020-panini-hoops-winter</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2048,11 +2033,6 @@
           <t>2021 Hoops Winter</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/basketball-cards-2021-panini-hoops-winter</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2181,7 +2161,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.sportscardspro.com/console/basketball-cards-2021-panini-eminence</t>
+          <t>https://www.sportscardspro.com/console/basketball-cards-2021-panini-eminence-autographs</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://www.sportscardspro.com/price-guide/download-custom?t=7f389d8e7c6dbb986abeec5f5789ac4a0a4cac15&amp;console-uids=G60812</t>
         </is>
       </c>
     </row>
@@ -2548,11 +2533,6 @@
           <t>2022 Hoops Winter</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/basketball-cards-2022-panini-hoops-winter</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2696,11 +2676,6 @@
           <t>2022 Panini Immaculate Collection</t>
         </is>
       </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/basketball-cards-2022-panini-immaculate-collection</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3048,11 +3023,6 @@
           <t>2023 Hoops Winter</t>
         </is>
       </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/basketball-cards-2023-panini-hoops-winter</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3162,11 +3132,6 @@
           <t>2023 Panini Immaculate Collection</t>
         </is>
       </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/basketball-cards-2023-panini-immaculate-collection</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3431,7 +3396,12 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://www.sportscardspro.com/console/basketball-cards-2023-panini-nba-top-class</t>
+          <t>https://www.sportscardspro.com/console/basketball-cards-2024-panini-nba-top-class</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>https://www.sportscardspro.com/price-guide/download-custom?t=7f389d8e7c6dbb986abeec5f5789ac4a0a4cac15&amp;console-uids=G76173</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3413,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://www.sportscardspro.com/console/basketball-cards-2023-topps-3</t>
+          <t>https://www.sportscardspro.com/console/basketball-cards-2023-topps-three</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>https://www.sportscardspro.com/price-guide/download-custom?t=7f389d8e7c6dbb986abeec5f5789ac4a0a4cac15&amp;console-uids=G80215</t>
         </is>
       </c>
     </row>
@@ -3487,11 +3462,6 @@
           <t>2023 Topps Chrome Sapphire Edition</t>
         </is>
       </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/basketball-cards-2023-topps-chrome-sapphire</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -3601,11 +3571,6 @@
           <t>2024 Hoops</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/basketball-cards-2024-panini-hoops</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -3630,11 +3595,6 @@
           <t>2024 Hoops Winter</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/basketball-cards-2024-panini-hoops-winter</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -3693,11 +3653,6 @@
           <t>2024 Panini Immaculate Collection</t>
         </is>
       </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/basketball-cards-2024-panini-immaculate-collection</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -3977,11 +3932,6 @@
           <t>2024 Topps Chrome Sapphire Edition</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>https://www.sportscardspro.com/console/basketball-cards-2024-topps-chrome-sapphire</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4144,7 +4094,12 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://www.sportscardspro.com/console/basketball-cards-2025-topps-3</t>
+          <t>https://www.sportscardspro.com/console/basketball-cards-2025-topps-three</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>https://www.sportscardspro.com/price-guide/download-custom?t=7f389d8e7c6dbb986abeec5f5789ac4a0a4cac15&amp;console-uids=G92512</t>
         </is>
       </c>
     </row>
